--- a/diseases/d045/2010-2014.xlsx
+++ b/diseases/d045/2010-2014.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2149,9 +2143,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3237,9 +3225,6 @@
       <c r="O16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.01864506151518533</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4325,9 +4307,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -5413,9 +5389,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6501,9 +6471,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7589,9 +7553,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7985,9 +7946,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8677,9 +8635,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -9073,9 +9028,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -9765,9 +9717,6 @@
       <c r="O52" t="n">
         <v>0</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
@@ -10161,9 +10110,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -10853,9 +10799,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -11249,9 +11192,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -11941,9 +11881,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -12337,9 +12274,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -13029,9 +12963,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -13425,9 +13356,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -14117,9 +14045,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -14513,9 +14438,6 @@
       <c r="O78" t="n">
         <v>0</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0</v>
       </c>
@@ -15205,9 +15127,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15601,9 +15520,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -16293,9 +16209,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -16689,9 +16602,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -17381,9 +17291,6 @@
       <c r="O94" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0</v>
       </c>
@@ -17777,9 +17684,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -18469,9 +18373,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -18865,9 +18766,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -19557,9 +19455,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19953,9 +19848,6 @@
       <c r="O108" t="n">
         <v>0</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0</v>
       </c>
@@ -20645,9 +20537,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -21041,9 +20930,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -21733,9 +21619,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -22129,9 +22012,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -22821,9 +22701,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -23217,9 +23094,6 @@
       <c r="O126" t="n">
         <v>2</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.04037982882182966</v>
       </c>
@@ -23909,9 +23783,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -24305,9 +24176,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.02018991441091483</v>
       </c>
@@ -24997,9 +24865,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.01855893231204766</v>
       </c>
@@ -25393,9 +25258,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -26085,9 +25947,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -26481,9 +26340,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -27173,9 +27029,6 @@
       <c r="O148" t="n">
         <v>0</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0</v>
       </c>
@@ -27569,9 +27422,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -28261,9 +28111,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -28657,9 +28504,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -29349,9 +29193,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -29745,9 +29586,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -30437,9 +30275,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30833,9 +30668,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -31525,9 +31357,6 @@
       <c r="O172" t="n">
         <v>0</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0</v>
       </c>
@@ -31921,9 +31750,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -32613,9 +32439,6 @@
       <c r="O178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -33009,9 +32832,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -33701,9 +33521,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -34097,9 +33914,6 @@
       <c r="O186" t="n">
         <v>1</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -34789,9 +34603,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -35185,9 +34996,6 @@
       <c r="O192" t="n">
         <v>1</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.01992644154105121</v>
       </c>
@@ -35877,9 +35685,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -36273,9 +36078,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -37409,9 +37211,6 @@
       <c r="O205" t="n">
         <v>0</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0</v>
       </c>
@@ -37805,9 +37604,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -39089,9 +38885,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -39485,9 +39278,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -40917,9 +40707,6 @@
       <c r="O226" t="n">
         <v>1</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.01847072892792288</v>
       </c>
@@ -41313,9 +41100,6 @@
       <c r="O228" t="n">
         <v>0</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0</v>
       </c>
@@ -42597,9 +42381,6 @@
       <c r="O236" t="n">
         <v>1</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -42993,9 +42774,6 @@
       <c r="O238" t="n">
         <v>1</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -44277,9 +44055,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -44821,9 +44596,6 @@
       <c r="O249" t="n">
         <v>0</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0</v>
       </c>
@@ -45957,9 +45729,6 @@
       <c r="O256" t="n">
         <v>0</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0</v>
       </c>
@@ -46501,9 +46270,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -47785,9 +47551,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -48181,9 +47944,6 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0</v>
       </c>
@@ -49465,9 +49225,6 @@
       <c r="O277" t="n">
         <v>1</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -49861,9 +49618,6 @@
       <c r="O279" t="n">
         <v>1</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -51293,9 +51047,6 @@
       <c r="O288" t="n">
         <v>0</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0</v>
       </c>
@@ -51689,9 +51440,6 @@
       <c r="O290" t="n">
         <v>0</v>
       </c>
-      <c r="Q290" t="n">
-        <v>0</v>
-      </c>
       <c r="R290" t="n">
         <v>0</v>
       </c>
@@ -52973,9 +52721,6 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -53369,9 +53114,6 @@
       <c r="O300" t="n">
         <v>0</v>
       </c>
-      <c r="Q300" t="n">
-        <v>0</v>
-      </c>
       <c r="R300" t="n">
         <v>0</v>
       </c>
@@ -54653,9 +54395,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -55049,9 +54788,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -56481,9 +56217,6 @@
       <c r="O319" t="n">
         <v>1</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -56877,9 +56610,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -58161,9 +57891,6 @@
       <c r="O329" t="n">
         <v>1</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>0.01838555351455483</v>
       </c>
@@ -58557,9 +58284,6 @@
       <c r="O331" t="n">
         <v>0</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0</v>
       </c>
@@ -59841,9 +59565,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -60385,9 +60106,6 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0</v>
       </c>
@@ -61669,9 +61387,6 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>0</v>
       </c>
@@ -62065,9 +61780,6 @@
       <c r="O352" t="n">
         <v>0</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0</v>
       </c>
@@ -63349,9 +63061,6 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
@@ -63745,9 +63454,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -65177,9 +64883,6 @@
       <c r="O371" t="n">
         <v>0</v>
       </c>
-      <c r="Q371" t="n">
-        <v>0</v>
-      </c>
       <c r="R371" t="n">
         <v>0</v>
       </c>
@@ -66461,9 +66164,6 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0</v>
       </c>
@@ -67745,9 +67445,6 @@
       <c r="O387" t="n">
         <v>0</v>
       </c>
-      <c r="Q387" t="n">
-        <v>0</v>
-      </c>
       <c r="R387" t="n">
         <v>0</v>
       </c>
@@ -69029,9 +68726,6 @@
       <c r="O395" t="n">
         <v>0</v>
       </c>
-      <c r="Q395" t="n">
-        <v>0</v>
-      </c>
       <c r="R395" t="n">
         <v>0</v>
       </c>
@@ -70461,9 +70155,6 @@
       <c r="O404" t="n">
         <v>0</v>
       </c>
-      <c r="Q404" t="n">
-        <v>0</v>
-      </c>
       <c r="R404" t="n">
         <v>0</v>
       </c>
@@ -71745,9 +71436,6 @@
       <c r="O412" t="n">
         <v>0</v>
       </c>
-      <c r="Q412" t="n">
-        <v>0</v>
-      </c>
       <c r="R412" t="n">
         <v>0</v>
       </c>
@@ -73029,9 +72717,6 @@
       <c r="O420" t="n">
         <v>0</v>
       </c>
-      <c r="Q420" t="n">
-        <v>0</v>
-      </c>
       <c r="R420" t="n">
         <v>0</v>
       </c>
@@ -74461,9 +74146,6 @@
       <c r="O429" t="n">
         <v>0</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>0</v>
       </c>
@@ -75745,9 +75427,6 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
       <c r="R437" t="n">
         <v>0</v>
       </c>
@@ -77177,9 +76856,6 @@
       <c r="O446" t="n">
         <v>0</v>
       </c>
-      <c r="Q446" t="n">
-        <v>0</v>
-      </c>
       <c r="R446" t="n">
         <v>0</v>
       </c>
@@ -78459,9 +78135,6 @@
         <v>0</v>
       </c>
       <c r="O454" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q454" t="n">
         <v>0</v>
       </c>
       <c r="R454" t="n">
